--- a/data/new_public_baths/0104_202606.xlsx
+++ b/data/new_public_baths/0104_202606.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A66CAFD-1CDA-4FAD-A0FE-E6EC951CB7C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B6EF90-9406-44EB-A72A-767FB5DB9AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{45B0F8AD-531B-483A-9043-79039076FE1D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="724">
   <si>
     <t>業務種別</t>
     <phoneticPr fontId="1"/>
@@ -2244,10 +2244,6 @@
   </si>
   <si>
     <t>ＬＡＶＥＳＳＯビル３階</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>087-821-4424</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3327,6 +3323,9 @@
   </sheetPr>
   <dimension ref="A1:O89"/>
   <sheetFormatPr defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="16.09765625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
@@ -3380,41 +3379,41 @@
         <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>482</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>671</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>672</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>29</v>
@@ -3425,43 +3424,43 @@
         <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>676</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>677</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>303</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M3" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>679</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>680</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>85</v>
@@ -3472,43 +3471,43 @@
         <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>684</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>685</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>303</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K4" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>688</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>689</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>29</v>
@@ -3519,43 +3518,43 @@
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>692</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>693</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K5" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>696</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>697</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>29</v>
@@ -3566,22 +3565,22 @@
         <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>701</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>702</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>19</v>
@@ -3593,10 +3592,10 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>703</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>704</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>85</v>
@@ -3607,43 +3606,43 @@
         <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>335</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>707</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>708</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M7" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>710</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>29</v>
@@ -3654,43 +3653,43 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>60</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>715</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>303</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M8" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>717</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>718</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>85</v>
@@ -3701,43 +3700,43 @@
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>721</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>722</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M9" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>723</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>724</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>29</v>
@@ -6739,11 +6738,9 @@
       <c r="E74" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="F74" s="1"/>
+      <c r="G74" s="1" t="s">
         <v>553</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>554</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>22</v>
@@ -6758,13 +6755,13 @@
         <v>536</v>
       </c>
       <c r="L74" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="M74" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="M74" s="1" t="s">
+      <c r="N74" s="1" t="s">
         <v>556</v>
-      </c>
-      <c r="N74" s="1" t="s">
-        <v>557</v>
       </c>
       <c r="O74" s="1" t="s">
         <v>29</v>
@@ -6775,43 +6772,43 @@
         <v>15</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="D75" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="E75" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F75" s="1" t="s">
+      <c r="G75" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>562</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="J75" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K75" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M75" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="L75" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M75" s="1" t="s">
+      <c r="N75" s="1" t="s">
         <v>565</v>
-      </c>
-      <c r="N75" s="1" t="s">
-        <v>566</v>
       </c>
       <c r="O75" s="1" t="s">
         <v>29</v>
@@ -6822,41 +6819,41 @@
         <v>15</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="D76" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>569</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F76" s="1"/>
       <c r="G76" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="J76" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K76" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M76" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="L76" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M76" s="1" t="s">
+      <c r="N76" s="1" t="s">
         <v>573</v>
-      </c>
-      <c r="N76" s="1" t="s">
-        <v>574</v>
       </c>
       <c r="O76" s="1" t="s">
         <v>29</v>
@@ -6867,41 +6864,41 @@
         <v>15</v>
       </c>
       <c r="B77" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="D77" s="1" t="s">
         <v>576</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>577</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F77" s="1"/>
       <c r="G77" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J77" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K77" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M77" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="L77" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M77" s="1" t="s">
+      <c r="N77" s="1" t="s">
         <v>581</v>
-      </c>
-      <c r="N77" s="1" t="s">
-        <v>582</v>
       </c>
       <c r="O77" s="1" t="s">
         <v>29</v>
@@ -6912,41 +6909,41 @@
         <v>15</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>60</v>
       </c>
       <c r="D78" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>584</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>585</v>
       </c>
       <c r="F78" s="1"/>
       <c r="G78" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="J78" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K78" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="L78" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="L78" s="1" t="s">
+      <c r="M78" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="M78" s="1" t="s">
+      <c r="N78" s="1" t="s">
         <v>590</v>
-      </c>
-      <c r="N78" s="1" t="s">
-        <v>591</v>
       </c>
       <c r="O78" s="1" t="s">
         <v>29</v>
@@ -6957,20 +6954,20 @@
         <v>15</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>60</v>
       </c>
       <c r="D79" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>593</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>594</v>
       </c>
       <c r="F79" s="1"/>
       <c r="G79" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>19</v>
@@ -6982,10 +6979,10 @@
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
       <c r="M79" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="N79" s="1" t="s">
         <v>596</v>
-      </c>
-      <c r="N79" s="1" t="s">
-        <v>597</v>
       </c>
       <c r="O79" s="1" t="s">
         <v>29</v>
@@ -6996,41 +6993,41 @@
         <v>15</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>60</v>
       </c>
       <c r="D80" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>600</v>
       </c>
       <c r="F80" s="1"/>
       <c r="G80" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J80" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="L80" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M80" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="N80" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="N80" s="1" t="s">
-        <v>604</v>
       </c>
       <c r="O80" s="1" t="s">
         <v>29</v>
@@ -7041,41 +7038,41 @@
         <v>15</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>60</v>
       </c>
       <c r="D81" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>607</v>
       </c>
       <c r="F81" s="1"/>
       <c r="G81" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J81" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="L81" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M81" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="O81" s="1" t="s">
         <v>29</v>
@@ -7086,43 +7083,43 @@
         <v>15</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>60</v>
       </c>
       <c r="D82" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="E82" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F82" s="1" t="s">
+      <c r="G82" s="1" t="s">
         <v>611</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>612</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J82" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K82" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="L82" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="L82" s="1" t="s">
+      <c r="M82" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="M82" s="1" t="s">
+      <c r="N82" s="1" t="s">
         <v>616</v>
-      </c>
-      <c r="N82" s="1" t="s">
-        <v>617</v>
       </c>
       <c r="O82" s="1" t="s">
         <v>29</v>
@@ -7133,43 +7130,43 @@
         <v>15</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>60</v>
       </c>
       <c r="D83" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F83" s="1" t="s">
+      <c r="G83" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>621</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="J83" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="L83" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M83" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="N83" s="1" t="s">
         <v>623</v>
-      </c>
-      <c r="N83" s="1" t="s">
-        <v>624</v>
       </c>
       <c r="O83" s="1" t="s">
         <v>29</v>
@@ -7180,22 +7177,22 @@
         <v>15</v>
       </c>
       <c r="B84" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="D84" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="E84" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="E84" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F84" s="1" t="s">
+      <c r="G84" s="1" t="s">
         <v>628</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>629</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>22</v>
@@ -7213,10 +7210,10 @@
         <v>19</v>
       </c>
       <c r="M84" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="N84" s="1" t="s">
         <v>630</v>
-      </c>
-      <c r="N84" s="1" t="s">
-        <v>631</v>
       </c>
       <c r="O84" s="1" t="s">
         <v>29</v>
@@ -7227,43 +7224,43 @@
         <v>15</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>60</v>
       </c>
       <c r="D85" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="F85" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="F85" s="1" t="s">
+      <c r="G85" s="1" t="s">
         <v>635</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>636</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="J85" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K85" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M85" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="L85" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M85" s="1" t="s">
+      <c r="N85" s="1" t="s">
         <v>639</v>
-      </c>
-      <c r="N85" s="1" t="s">
-        <v>640</v>
       </c>
       <c r="O85" s="1" t="s">
         <v>29</v>
@@ -7274,43 +7271,43 @@
         <v>15</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>521</v>
       </c>
       <c r="D86" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="E86" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F86" s="1" t="s">
+      <c r="G86" s="1" t="s">
         <v>643</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>644</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="J86" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K86" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M86" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="L86" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M86" s="1" t="s">
+      <c r="N86" s="1" t="s">
         <v>647</v>
-      </c>
-      <c r="N86" s="1" t="s">
-        <v>648</v>
       </c>
       <c r="O86" s="1" t="s">
         <v>29</v>
@@ -7321,41 +7318,41 @@
         <v>15</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>60</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F87" s="1"/>
       <c r="G87" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="J87" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="L87" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M87" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="N87" s="1" t="s">
         <v>652</v>
-      </c>
-      <c r="N87" s="1" t="s">
-        <v>653</v>
       </c>
       <c r="O87" s="1" t="s">
         <v>29</v>
@@ -7366,41 +7363,41 @@
         <v>15</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>60</v>
       </c>
       <c r="D88" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>655</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>656</v>
       </c>
       <c r="F88" s="1"/>
       <c r="G88" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J88" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="L88" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M88" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="N88" s="1" t="s">
         <v>657</v>
-      </c>
-      <c r="N88" s="1" t="s">
-        <v>658</v>
       </c>
       <c r="O88" s="1" t="s">
         <v>29</v>
@@ -7411,41 +7408,41 @@
         <v>15</v>
       </c>
       <c r="B89" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="D89" s="1" t="s">
         <v>660</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>661</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F89" s="1"/>
       <c r="G89" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="J89" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K89" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M89" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="L89" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M89" s="1" t="s">
+      <c r="N89" s="1" t="s">
         <v>665</v>
-      </c>
-      <c r="N89" s="1" t="s">
-        <v>666</v>
       </c>
       <c r="O89" s="1" t="s">
         <v>29</v>
